--- a/примеры.xlsx
+++ b/примеры.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grish\OneDrive\Рабочий стол\учба\8 семестр\Мальков Александр\ReferatMalkov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5EDF26-8DB8-434A-ACD5-AEF5E64E4DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2945130C-ECC1-4352-B56E-4542194AE768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5370" yWindow="5340" windowWidth="21600" windowHeight="11295" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="one hot" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="70">
   <si>
     <t>Город</t>
   </si>
@@ -207,6 +207,39 @@
   </si>
   <si>
     <t>0.01</t>
+  </si>
+  <si>
+    <t>Таблица 4. Результаты тестирования на датасете Historical_Pandemic_Epidemic</t>
+  </si>
+  <si>
+    <t>(11 категориальных признаков, 123 уникальных категории, 50 записей, целевая: оценочные случаи)</t>
+  </si>
+  <si>
+    <t>Корреляция Пирсона</t>
+  </si>
+  <si>
+    <t>Корреляция Спирмена</t>
+  </si>
+  <si>
+    <t>Потеря инф, (%)</t>
+  </si>
+  <si>
+    <t>Среднее качество</t>
+  </si>
+  <si>
+    <t>65.30%</t>
+  </si>
+  <si>
+    <t>47.82%</t>
+  </si>
+  <si>
+    <t>13.00%</t>
+  </si>
+  <si>
+    <t>11.76%</t>
+  </si>
+  <si>
+    <t>7.86%</t>
   </si>
 </sst>
 </file>
@@ -1182,7 +1215,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0103929C-118D-46D8-A9FD-2A0A4FBD2EBE}">
-  <dimension ref="B2:H20"/>
+  <dimension ref="B2:O30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -1190,19 +1223,29 @@
     <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>34</v>
       </c>
@@ -1224,8 +1267,14 @@
       <c r="H4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>41</v>
       </c>
@@ -1247,8 +1296,14 @@
       <c r="H5" s="5">
         <v>0.71</v>
       </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>42</v>
       </c>
@@ -1270,8 +1325,14 @@
       <c r="H6" s="5">
         <v>0.68</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>43</v>
       </c>
@@ -1293,8 +1354,14 @@
       <c r="H7" s="5">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>44</v>
       </c>
@@ -1316,8 +1383,14 @@
       <c r="H8" s="5">
         <v>0.04</v>
       </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>45</v>
       </c>
@@ -1340,17 +1413,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -1372,8 +1445,14 @@
       <c r="H15" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="N15" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>41</v>
       </c>
@@ -1395,8 +1474,14 @@
       <c r="H16" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
+        <v>41</v>
+      </c>
+      <c r="O16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>43</v>
       </c>
@@ -1418,8 +1503,14 @@
       <c r="H17" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="N17" t="s">
+        <v>42</v>
+      </c>
+      <c r="O17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>45</v>
       </c>
@@ -1441,8 +1532,14 @@
       <c r="H18" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="N18" t="s">
+        <v>43</v>
+      </c>
+      <c r="O18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>44</v>
       </c>
@@ -1464,8 +1561,14 @@
       <c r="H19" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="N19" t="s">
+        <v>44</v>
+      </c>
+      <c r="O19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>42</v>
       </c>
@@ -1486,6 +1589,178 @@
       </c>
       <c r="H20" t="s">
         <v>55</v>
+      </c>
+      <c r="N20" t="s">
+        <v>45</v>
+      </c>
+      <c r="O20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="5">
+        <v>88.99</v>
+      </c>
+      <c r="D26" s="5">
+        <v>11.01</v>
+      </c>
+      <c r="E26" s="5">
+        <v>123</v>
+      </c>
+      <c r="F26" s="5">
+        <v>28</v>
+      </c>
+      <c r="G26" s="5">
+        <v>0.82</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="5">
+        <v>53.46</v>
+      </c>
+      <c r="D27" s="5">
+        <v>46.54</v>
+      </c>
+      <c r="E27" s="5">
+        <v>123</v>
+      </c>
+      <c r="F27" s="5">
+        <v>22</v>
+      </c>
+      <c r="G27" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="H27" s="5">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I27" s="5">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="5">
+        <v>12.45</v>
+      </c>
+      <c r="D28" s="5">
+        <v>87.55</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5">
+        <v>18</v>
+      </c>
+      <c r="G28" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="H28" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="I28" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="5">
+        <v>9.08</v>
+      </c>
+      <c r="D29" s="5">
+        <v>90.92</v>
+      </c>
+      <c r="E29" s="5">
+        <v>123</v>
+      </c>
+      <c r="F29" s="5">
+        <v>25</v>
+      </c>
+      <c r="G29" s="5">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="H29" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="I29" s="5">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="5">
+        <v>5</v>
+      </c>
+      <c r="D30" s="5">
+        <v>95</v>
+      </c>
+      <c r="E30" s="5">
+        <v>123</v>
+      </c>
+      <c r="F30" s="5">
+        <v>20</v>
+      </c>
+      <c r="G30" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="H30" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="I30" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
